--- a/artfynd/A 44916-2024 artfynd.xlsx
+++ b/artfynd/A 44916-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>74859094</v>
       </c>
       <c r="B2" t="n">
-        <v>98536</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100790</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>563761.8525366654</v>
+        <v>563762</v>
       </c>
       <c r="R2" t="n">
-        <v>6275130.369290748</v>
+        <v>6275130</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>1985-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1985-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">

--- a/artfynd/A 44916-2024 artfynd.xlsx
+++ b/artfynd/A 44916-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74859094</v>
       </c>
       <c r="B2" t="n">
-        <v>100790</v>
+        <v>100796</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44916-2024 artfynd.xlsx
+++ b/artfynd/A 44916-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74859094</v>
       </c>
       <c r="B2" t="n">
-        <v>100796</v>
+        <v>100797</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44916-2024 artfynd.xlsx
+++ b/artfynd/A 44916-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74859094</v>
       </c>
       <c r="B2" t="n">
-        <v>100797</v>
+        <v>100824</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44916-2024 artfynd.xlsx
+++ b/artfynd/A 44916-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74859094</v>
       </c>
       <c r="B2" t="n">
-        <v>100824</v>
+        <v>100830</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44916-2024 artfynd.xlsx
+++ b/artfynd/A 44916-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74859094</v>
       </c>
       <c r="B2" t="n">
-        <v>100830</v>
+        <v>100837</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44916-2024 artfynd.xlsx
+++ b/artfynd/A 44916-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74859094</v>
       </c>
       <c r="B2" t="n">
-        <v>100837</v>
+        <v>100841</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44916-2024 artfynd.xlsx
+++ b/artfynd/A 44916-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74859094</v>
       </c>
       <c r="B2" t="n">
-        <v>100841</v>
+        <v>100848</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44916-2024 artfynd.xlsx
+++ b/artfynd/A 44916-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74859094</v>
       </c>
       <c r="B2" t="n">
-        <v>100851</v>
+        <v>100856</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44916-2024 artfynd.xlsx
+++ b/artfynd/A 44916-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74859094</v>
       </c>
       <c r="B2" t="n">
-        <v>100856</v>
+        <v>100864</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44916-2024 artfynd.xlsx
+++ b/artfynd/A 44916-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74859094</v>
       </c>
       <c r="B2" t="n">
-        <v>100864</v>
+        <v>100874</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44916-2024 artfynd.xlsx
+++ b/artfynd/A 44916-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>74859094</v>
+        <v>74859093</v>
       </c>
       <c r="B2" t="n">
-        <v>100874</v>
+        <v>101344</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -706,7 +706,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ryabacken (vid Tvärskog) 325 m SO--OSO, Sm</t>
+          <t>Ryabacken (vid Tvärskog) 325 m SO-OSO, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -750,7 +750,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 4G5c 1543. SOM: Pulsatilla vernalis. LEG: Thomas Karlsson</t>
+          <t>Smålands flora 2007: KOO: 4G5c 1543. SOM: Pulsatilla vernalis. LEG: Thomas Karlsson. KOM: +</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,12 +789,7 @@
         <v>113257232</v>
       </c>
       <c r="B3" t="n">
-        <v>90954</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92567</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 44916-2024 artfynd.xlsx
+++ b/artfynd/A 44916-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74859093</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -881,8 +891,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113257232</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>